--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,1096 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131431419</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Väsby, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>549456</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6411335</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131431346</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Väsby, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>549435</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6411436</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131431021</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väsby, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>549321</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6411355</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131431358</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väsby, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>549458</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6411190</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131431043</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Väsby, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>549435</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6411307</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131430967</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Väsby, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>549451</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6411406</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131431098</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Väsby, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>549469</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6411394</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131431062</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Väsby, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>549420</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6411427</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131431405</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Väsby, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>549464</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6411279</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131431566</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Väsby, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>549436</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6411426</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -1351,42 +1351,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131430967</v>
+        <v>131431098</v>
       </c>
       <c r="B8" t="n">
-        <v>57076</v>
+        <v>99022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549451</v>
+        <v>549469</v>
       </c>
       <c r="R8" t="n">
-        <v>6411406</v>
+        <v>6411394</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,6 +1442,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1456,46 +1461,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131431098</v>
+        <v>131430967</v>
       </c>
       <c r="B9" t="n">
-        <v>99022</v>
+        <v>57076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549469</v>
+        <v>549451</v>
       </c>
       <c r="R9" t="n">
-        <v>6411394</v>
+        <v>6411406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1548,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131431346</v>
+        <v>131431021</v>
       </c>
       <c r="B4" t="n">
         <v>99022</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549435</v>
+        <v>549321</v>
       </c>
       <c r="R4" t="n">
-        <v>6411436</v>
+        <v>6411355</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131431021</v>
+        <v>131431346</v>
       </c>
       <c r="B5" t="n">
         <v>99022</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549321</v>
+        <v>549435</v>
       </c>
       <c r="R5" t="n">
-        <v>6411355</v>
+        <v>6411436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1241,46 +1241,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131431043</v>
+        <v>131430967</v>
       </c>
       <c r="B7" t="n">
-        <v>99022</v>
+        <v>57076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549435</v>
+        <v>549451</v>
       </c>
       <c r="R7" t="n">
-        <v>6411307</v>
+        <v>6411406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1328,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1351,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131431098</v>
+        <v>131431043</v>
       </c>
       <c r="B8" t="n">
         <v>99022</v>
@@ -1381,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1398,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549469</v>
+        <v>549435</v>
       </c>
       <c r="R8" t="n">
-        <v>6411394</v>
+        <v>6411307</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,42 +1456,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131430967</v>
+        <v>131431098</v>
       </c>
       <c r="B9" t="n">
-        <v>57076</v>
+        <v>99022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1504,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549451</v>
+        <v>549469</v>
       </c>
       <c r="R9" t="n">
-        <v>6411406</v>
+        <v>6411394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,6 +1547,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131431419</v>
       </c>
       <c r="B3" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131431021</v>
+        <v>131431346</v>
       </c>
       <c r="B4" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549321</v>
+        <v>549435</v>
       </c>
       <c r="R4" t="n">
-        <v>6411355</v>
+        <v>6411436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131431346</v>
+        <v>131431021</v>
       </c>
       <c r="B5" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549435</v>
+        <v>549321</v>
       </c>
       <c r="R5" t="n">
-        <v>6411436</v>
+        <v>6411355</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,7 +1134,7 @@
         <v>131431358</v>
       </c>
       <c r="B6" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,42 +1241,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131430967</v>
+        <v>131431043</v>
       </c>
       <c r="B7" t="n">
-        <v>57076</v>
+        <v>99023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549451</v>
+        <v>549435</v>
       </c>
       <c r="R7" t="n">
-        <v>6411406</v>
+        <v>6411307</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,6 +1332,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1346,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131431043</v>
+        <v>131431098</v>
       </c>
       <c r="B8" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1381,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1393,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549435</v>
+        <v>549469</v>
       </c>
       <c r="R8" t="n">
-        <v>6411307</v>
+        <v>6411394</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,46 +1461,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131431098</v>
+        <v>131430967</v>
       </c>
       <c r="B9" t="n">
-        <v>99022</v>
+        <v>57076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549469</v>
+        <v>549451</v>
       </c>
       <c r="R9" t="n">
-        <v>6411394</v>
+        <v>6411406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1548,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>131431062</v>
       </c>
       <c r="B10" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,46 +1676,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131431405</v>
+        <v>131431566</v>
       </c>
       <c r="B11" t="n">
-        <v>99022</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1723,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549464</v>
+        <v>549436</v>
       </c>
       <c r="R11" t="n">
-        <v>6411279</v>
+        <v>6411426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1763,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,42 +1781,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131431566</v>
+        <v>131431405</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>99023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1829,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549436</v>
+        <v>549464</v>
       </c>
       <c r="R12" t="n">
-        <v>6411426</v>
+        <v>6411279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,6 +1872,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -1676,42 +1676,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131431566</v>
+        <v>131431405</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>99023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1719,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549436</v>
+        <v>549464</v>
       </c>
       <c r="R11" t="n">
-        <v>6411426</v>
+        <v>6411279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,6 +1767,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1781,46 +1786,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131431405</v>
+        <v>131431566</v>
       </c>
       <c r="B12" t="n">
-        <v>99023</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1828,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549464</v>
+        <v>549436</v>
       </c>
       <c r="R12" t="n">
-        <v>6411279</v>
+        <v>6411426</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,7 +1873,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131431419</v>
       </c>
       <c r="B3" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>131431346</v>
       </c>
       <c r="B4" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131431021</v>
       </c>
       <c r="B5" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>131431358</v>
       </c>
       <c r="B6" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,46 +1241,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131431043</v>
+        <v>131430967</v>
       </c>
       <c r="B7" t="n">
-        <v>99023</v>
+        <v>57079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549435</v>
+        <v>549451</v>
       </c>
       <c r="R7" t="n">
-        <v>6411307</v>
+        <v>6411406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1328,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1351,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131431098</v>
+        <v>131431043</v>
       </c>
       <c r="B8" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1398,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549469</v>
+        <v>549435</v>
       </c>
       <c r="R8" t="n">
-        <v>6411394</v>
+        <v>6411307</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,42 +1456,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131430967</v>
+        <v>131431098</v>
       </c>
       <c r="B9" t="n">
-        <v>57076</v>
+        <v>99026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1504,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549451</v>
+        <v>549469</v>
       </c>
       <c r="R9" t="n">
-        <v>6411406</v>
+        <v>6411394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,6 +1547,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>131431062</v>
       </c>
       <c r="B10" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,46 +1676,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131431405</v>
+        <v>131431566</v>
       </c>
       <c r="B11" t="n">
-        <v>99023</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1723,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549464</v>
+        <v>549436</v>
       </c>
       <c r="R11" t="n">
-        <v>6411279</v>
+        <v>6411426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1763,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,42 +1781,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131431566</v>
+        <v>131431405</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>99026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1829,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549436</v>
+        <v>549464</v>
       </c>
       <c r="R12" t="n">
-        <v>6411426</v>
+        <v>6411279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,6 +1872,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131431419</v>
       </c>
       <c r="B3" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>131431346</v>
       </c>
       <c r="B4" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131431021</v>
       </c>
       <c r="B5" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>131431358</v>
       </c>
       <c r="B6" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>131430967</v>
       </c>
       <c r="B7" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131431043</v>
       </c>
       <c r="B8" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131431098</v>
       </c>
       <c r="B9" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>131431062</v>
       </c>
       <c r="B10" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>131431566</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>131431405</v>
       </c>
       <c r="B12" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131431419</v>
       </c>
       <c r="B3" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131431346</v>
+        <v>131431021</v>
       </c>
       <c r="B4" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549435</v>
+        <v>549321</v>
       </c>
       <c r="R4" t="n">
-        <v>6411436</v>
+        <v>6411355</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131431021</v>
+        <v>131431346</v>
       </c>
       <c r="B5" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549321</v>
+        <v>549435</v>
       </c>
       <c r="R5" t="n">
-        <v>6411355</v>
+        <v>6411436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,7 +1134,7 @@
         <v>131431358</v>
       </c>
       <c r="B6" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>131430967</v>
       </c>
       <c r="B7" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131431043</v>
       </c>
       <c r="B8" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131431098</v>
       </c>
       <c r="B9" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>131431062</v>
       </c>
       <c r="B10" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>131431566</v>
       </c>
       <c r="B11" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>131431405</v>
       </c>
       <c r="B12" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -1241,42 +1241,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131430967</v>
+        <v>131431043</v>
       </c>
       <c r="B7" t="n">
-        <v>57086</v>
+        <v>99033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549451</v>
+        <v>549435</v>
       </c>
       <c r="R7" t="n">
-        <v>6411406</v>
+        <v>6411307</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,6 +1332,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1346,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131431043</v>
+        <v>131431098</v>
       </c>
       <c r="B8" t="n">
         <v>99033</v>
@@ -1376,7 +1381,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1393,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549435</v>
+        <v>549469</v>
       </c>
       <c r="R8" t="n">
-        <v>6411307</v>
+        <v>6411394</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,46 +1461,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131431098</v>
+        <v>131430967</v>
       </c>
       <c r="B9" t="n">
-        <v>99033</v>
+        <v>57086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549469</v>
+        <v>549451</v>
       </c>
       <c r="R9" t="n">
-        <v>6411394</v>
+        <v>6411406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1548,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131431021</v>
+        <v>131431346</v>
       </c>
       <c r="B4" t="n">
         <v>99033</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549321</v>
+        <v>549435</v>
       </c>
       <c r="R4" t="n">
-        <v>6411355</v>
+        <v>6411436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131431346</v>
+        <v>131431021</v>
       </c>
       <c r="B5" t="n">
         <v>99033</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549435</v>
+        <v>549321</v>
       </c>
       <c r="R5" t="n">
-        <v>6411436</v>
+        <v>6411355</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1241,46 +1241,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131431043</v>
+        <v>131430967</v>
       </c>
       <c r="B7" t="n">
-        <v>99033</v>
+        <v>57086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549435</v>
+        <v>549451</v>
       </c>
       <c r="R7" t="n">
-        <v>6411307</v>
+        <v>6411406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1328,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1351,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131431098</v>
+        <v>131431043</v>
       </c>
       <c r="B8" t="n">
         <v>99033</v>
@@ -1381,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1398,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549469</v>
+        <v>549435</v>
       </c>
       <c r="R8" t="n">
-        <v>6411394</v>
+        <v>6411307</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,42 +1456,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131430967</v>
+        <v>131431098</v>
       </c>
       <c r="B9" t="n">
-        <v>57086</v>
+        <v>99033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1504,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549451</v>
+        <v>549469</v>
       </c>
       <c r="R9" t="n">
-        <v>6411406</v>
+        <v>6411394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,6 +1547,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131431419</v>
       </c>
       <c r="B3" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>131431346</v>
       </c>
       <c r="B4" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131431021</v>
       </c>
       <c r="B5" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>131431358</v>
       </c>
       <c r="B6" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131431043</v>
       </c>
       <c r="B8" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131431098</v>
       </c>
       <c r="B9" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>131431062</v>
       </c>
       <c r="B10" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>131431405</v>
       </c>
       <c r="B12" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131431419</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>131431346</v>
       </c>
       <c r="B4" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131431021</v>
       </c>
       <c r="B5" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>131431358</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>131430967</v>
       </c>
       <c r="B7" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131431043</v>
       </c>
       <c r="B8" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131431098</v>
       </c>
       <c r="B9" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>131431062</v>
       </c>
       <c r="B10" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>131431566</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>131431405</v>
       </c>
       <c r="B12" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131431419</v>
       </c>
       <c r="B3" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>131431346</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131431021</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>131431358</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>131430967</v>
       </c>
       <c r="B7" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131431043</v>
       </c>
       <c r="B8" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131431098</v>
       </c>
       <c r="B9" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>131431062</v>
       </c>
       <c r="B10" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>131431566</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>131431405</v>
       </c>
       <c r="B12" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8356-2026 artfynd.xlsx
+++ b/artfynd/A 8356-2026 artfynd.xlsx
@@ -1676,42 +1676,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131431566</v>
+        <v>131431405</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1719,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549436</v>
+        <v>549464</v>
       </c>
       <c r="R11" t="n">
-        <v>6411426</v>
+        <v>6411279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,6 +1767,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1781,46 +1786,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131431405</v>
+        <v>131431566</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1828,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549464</v>
+        <v>549436</v>
       </c>
       <c r="R12" t="n">
-        <v>6411279</v>
+        <v>6411426</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,7 +1873,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
